--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T09:04:56+00:00</t>
+    <t>2024-02-19T13:34:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T13:34:28+00:00</t>
+    <t>2024-02-19T13:42:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-19T13:42:29+00:00</t>
+    <t>2024-03-04T16:55:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -780,7 +780,7 @@
 </t>
   </si>
   <si>
-    <t>La discipline déterminant la nature de l’activité (disciplineEquipementSociale).</t>
+    <t>Broad category of service being performed or delivered</t>
   </si>
   <si>
     <t>Identifies the broad category of service being performed or delivered.</t>
@@ -808,7 +808,7 @@
 </t>
   </si>
   <si>
-    <t>Type of service that may be delivered or performed</t>
+    <t>La discipline déterminant la nature de l’activité (disciplineEquipementSociale).</t>
   </si>
   <si>
     <t>The specific type of service that may be delivered or performed.</t>
@@ -4462,7 +4462,7 @@
         <v>77</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>75</v>
@@ -4570,7 +4570,7 @@
         <v>77</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>75</v>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-04T16:55:03+00:00</t>
+    <t>2024-03-05T15:34:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-05T15:34:40+00:00</t>
+    <t>2024-03-06T10:45:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$64</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AL$72</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2208" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2482" uniqueCount="458">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-06T10:45:14+00:00</t>
+    <t>2024-03-07T10:27:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -721,6 +721,195 @@
     <t>Identifiant fonctionnel, numéro d'autorisation ARHGOS (numeroAutorisationARHGOS).</t>
   </si>
   <si>
+    <t>HealthcareService.identifier:numAutorisationArhgos.id</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier.id</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier:numAutorisationArhgos.extension</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier.extension</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier:numAutorisationArhgos.use</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier.use</t>
+  </si>
+  <si>
+    <t>usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+  </si>
+  <si>
+    <t>required</t>
+  </si>
+  <si>
+    <t>Identifies the purpose for this identifier, if known .</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
+  </si>
+  <si>
+    <t>Identifier.use</t>
+  </si>
+  <si>
+    <t>Role.code or implied by context</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier:numAutorisationArhgos.type</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier.type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Description of identifier</t>
+  </si>
+  <si>
+    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+  </si>
+  <si>
+    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+  </si>
+  <si>
+    <t>Identifier.type</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier:numAutorisationArhgos.system</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier.system</t>
+  </si>
+  <si>
+    <t>The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+  </si>
+  <si>
+    <t>Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+  </si>
+  <si>
+    <t>https://arhgos.ars.sante.fr/</t>
+  </si>
+  <si>
+    <t>http://www.acme.com/identifiers/patient</t>
+  </si>
+  <si>
+    <t>Identifier.system</t>
+  </si>
+  <si>
+    <t>II.root or Role.id.root</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier:numAutorisationArhgos.value</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier.value</t>
+  </si>
+  <si>
+    <t>The value that is unique</t>
+  </si>
+  <si>
+    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+  </si>
+  <si>
+    <t>123456</t>
+  </si>
+  <si>
+    <t>Identifier.value</t>
+  </si>
+  <si>
+    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier:numAutorisationArhgos.period</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier.period</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Period
+</t>
+  </si>
+  <si>
+    <t>Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>Time period during which identifier is/was valid for use.</t>
+  </si>
+  <si>
+    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
+Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
+  </si>
+  <si>
+    <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
+  </si>
+  <si>
+    <t>Role.effectiveTime or implied by context</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier:numAutorisationArhgos.assigner</t>
+  </si>
+  <si>
+    <t>HealthcareService.identifier.assigner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(Organization)
+</t>
+  </si>
+  <si>
+    <t>Organization that issued id (may be just text)</t>
+  </si>
+  <si>
+    <t>Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+  </si>
+  <si>
+    <t>Identifier.assigner</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
+    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
+  </si>
+  <si>
     <t>HealthcareService.active</t>
   </si>
   <si>
@@ -762,10 +951,6 @@
     <t>This property is recommended to be the same as the Location's managingOrganization, and if not provided should be interpreted as such. If the Location does not have a managing Organization, then this property should be populated.</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
     <t>.scopingRole.Organization</t>
   </si>
   <si>
@@ -776,10 +961,6 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
     <t>Broad category of service being performed or delivered</t>
   </si>
   <si>
@@ -817,9 +998,6 @@
     <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
   </si>
   <si>
-    <t>required</t>
-  </si>
-  <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J136-DisciplineEquipementSocial-RASS/FHIR/JDV-J136-DisciplineEquipementSocial-RASS</t>
   </si>
   <si>
@@ -1232,22 +1410,10 @@
     <t>HealthcareService.notAvailable.during</t>
   </si>
   <si>
-    <t xml:space="preserve">Period
-</t>
-  </si>
-  <si>
     <t>Service not available from this date</t>
   </si>
   <si>
     <t>Service is not available (seasonally or for a public holiday) from this date.</t>
-  </si>
-  <si>
-    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
-Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
-  </si>
-  <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
   </si>
   <si>
     <t>HealthcareService.availabilityExceptions</t>
@@ -1589,7 +1755,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AL64"/>
+  <dimension ref="A1:AL72"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="63.55078125" customWidth="true" bestFit="true"/>
@@ -1611,7 +1777,7 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.953125" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="38.2265625" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
@@ -1627,7 +1793,7 @@
     <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="72.5234375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="102.6171875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="36.91796875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
@@ -4230,7 +4396,7 @@
         <v>225</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4247,30 +4413,26 @@
         <v>75</v>
       </c>
       <c r="I25" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>226</v>
+        <v>100</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>227</v>
+        <v>101</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>229</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="Q25" t="s" s="2">
-        <v>230</v>
-      </c>
+      <c r="Q25" s="2"/>
       <c r="R25" t="s" s="2">
         <v>75</v>
       </c>
@@ -4314,7 +4476,7 @@
         <v>75</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>225</v>
+        <v>103</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -4323,35 +4485,35 @@
         <v>84</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>231</v>
+        <v>104</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>232</v>
+        <v>75</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>233</v>
+        <v>227</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>75</v>
@@ -4360,19 +4522,19 @@
         <v>75</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>234</v>
+        <v>107</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>235</v>
+        <v>108</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>236</v>
+        <v>109</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>237</v>
+        <v>110</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4410,34 +4572,34 @@
         <v>75</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>233</v>
+        <v>114</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>238</v>
+        <v>115</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>239</v>
+        <v>98</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>75</v>
@@ -4445,44 +4607,46 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>241</v>
+        <v>75</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J27" t="s" s="2">
         <v>85</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>242</v>
+        <v>168</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>245</v>
-      </c>
-      <c r="O27" s="2"/>
+        <v>233</v>
+      </c>
+      <c r="O27" t="s" s="2">
+        <v>234</v>
+      </c>
       <c r="P27" t="s" s="2">
         <v>75</v>
       </c>
@@ -4506,13 +4670,13 @@
         <v>75</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>158</v>
+        <v>235</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="Z27" t="s" s="2">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="AA27" t="s" s="2">
         <v>75</v>
@@ -4530,13 +4694,13 @@
         <v>75</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>96</v>
@@ -4545,32 +4709,32 @@
         <v>97</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>249</v>
+        <v>75</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>251</v>
+        <v>75</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>75</v>
@@ -4582,15 +4746,17 @@
         <v>242</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>254</v>
-      </c>
-      <c r="O28" s="2"/>
+        <v>245</v>
+      </c>
+      <c r="O28" t="s" s="2">
+        <v>246</v>
+      </c>
       <c r="P28" t="s" s="2">
         <v>75</v>
       </c>
@@ -4614,11 +4780,13 @@
         <v>75</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="Y28" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>247</v>
+      </c>
       <c r="Z28" t="s" s="2">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>75</v>
@@ -4636,13 +4804,13 @@
         <v>75</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>96</v>
@@ -4651,7 +4819,7 @@
         <v>97</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>257</v>
+        <v>239</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>75</v>
@@ -4659,10 +4827,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4670,10 +4838,10 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>75</v>
@@ -4685,18 +4853,20 @@
         <v>85</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>242</v>
+        <v>133</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="N29" t="s" s="2">
         <v>254</v>
       </c>
-      <c r="O29" s="2"/>
+      <c r="O29" t="s" s="2">
+        <v>255</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>75</v>
       </c>
@@ -4705,10 +4875,10 @@
         <v>75</v>
       </c>
       <c r="S29" t="s" s="2">
-        <v>75</v>
+        <v>256</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>75</v>
+        <v>257</v>
       </c>
       <c r="U29" t="s" s="2">
         <v>75</v>
@@ -4720,13 +4890,13 @@
         <v>75</v>
       </c>
       <c r="X29" t="s" s="2">
-        <v>172</v>
+        <v>75</v>
       </c>
       <c r="Y29" t="s" s="2">
-        <v>261</v>
+        <v>75</v>
       </c>
       <c r="Z29" t="s" s="2">
-        <v>262</v>
+        <v>75</v>
       </c>
       <c r="AA29" t="s" s="2">
         <v>75</v>
@@ -4750,7 +4920,7 @@
         <v>76</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>96</v>
@@ -4759,7 +4929,7 @@
         <v>97</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>75</v>
@@ -4767,10 +4937,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4781,7 +4951,7 @@
         <v>76</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>75</v>
@@ -4793,16 +4963,16 @@
         <v>85</v>
       </c>
       <c r="K30" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>262</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>263</v>
+      </c>
+      <c r="N30" t="s" s="2">
         <v>264</v>
-      </c>
-      <c r="L30" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="M30" t="s" s="2">
-        <v>266</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>267</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -4816,7 +4986,7 @@
         <v>75</v>
       </c>
       <c r="T30" t="s" s="2">
-        <v>75</v>
+        <v>265</v>
       </c>
       <c r="U30" t="s" s="2">
         <v>75</v>
@@ -4852,33 +5022,33 @@
         <v>75</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>238</v>
+        <v>97</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>269</v>
+        <v>75</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4901,7 +5071,7 @@
         <v>85</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>100</v>
+        <v>270</v>
       </c>
       <c r="L31" t="s" s="2">
         <v>271</v>
@@ -4960,7 +5130,7 @@
         <v>75</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -4972,10 +5142,10 @@
         <v>96</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>97</v>
+        <v>275</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AL31" t="s" s="2">
         <v>75</v>
@@ -4983,10 +5153,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5009,16 +5179,16 @@
         <v>85</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>100</v>
+        <v>279</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5068,7 +5238,7 @@
         <v>75</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -5080,10 +5250,10 @@
         <v>96</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>97</v>
+        <v>284</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>75</v>
@@ -5091,10 +5261,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5111,28 +5281,30 @@
         <v>75</v>
       </c>
       <c r="I33" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J33" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="Q33" s="2"/>
+      <c r="Q33" t="s" s="2">
+        <v>291</v>
+      </c>
       <c r="R33" t="s" s="2">
         <v>75</v>
       </c>
@@ -5176,7 +5348,7 @@
         <v>75</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -5191,18 +5363,18 @@
         <v>97</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>285</v>
+        <v>292</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>75</v>
+        <v>293</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5225,16 +5397,16 @@
         <v>85</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5284,7 +5456,7 @@
         <v>75</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -5296,10 +5468,10 @@
         <v>96</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>292</v>
+        <v>299</v>
       </c>
       <c r="AL34" t="s" s="2">
         <v>75</v>
@@ -5307,14 +5479,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>75</v>
+        <v>301</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5330,19 +5502,19 @@
         <v>75</v>
       </c>
       <c r="J35" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>294</v>
+        <v>242</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5368,13 +5540,13 @@
         <v>75</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>75</v>
+        <v>158</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>75</v>
+        <v>305</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>75</v>
+        <v>306</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>75</v>
@@ -5392,7 +5564,7 @@
         <v>75</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -5404,25 +5576,25 @@
         <v>96</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>298</v>
+        <v>97</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>75</v>
+        <v>308</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
-        <v>75</v>
+        <v>310</v>
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
@@ -5432,25 +5604,25 @@
         <v>77</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>75</v>
       </c>
       <c r="J36" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
@@ -5476,13 +5648,11 @@
         <v>75</v>
       </c>
       <c r="X36" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y36" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>235</v>
+      </c>
+      <c r="Y36" s="2"/>
       <c r="Z36" t="s" s="2">
-        <v>75</v>
+        <v>314</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>75</v>
@@ -5500,7 +5670,7 @@
         <v>75</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -5512,10 +5682,10 @@
         <v>96</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>238</v>
+        <v>97</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>75</v>
@@ -5523,10 +5693,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5546,19 +5716,19 @@
         <v>75</v>
       </c>
       <c r="J37" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K37" t="s" s="2">
         <v>242</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>306</v>
+        <v>317</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -5584,13 +5754,13 @@
         <v>75</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>75</v>
@@ -5608,7 +5778,7 @@
         <v>75</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -5623,7 +5793,7 @@
         <v>97</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="AL37" t="s" s="2">
         <v>75</v>
@@ -5631,10 +5801,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5648,24 +5818,26 @@
         <v>77</v>
       </c>
       <c r="H38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J38" t="s" s="2">
         <v>85</v>
       </c>
-      <c r="I38" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J38" t="s" s="2">
-        <v>75</v>
-      </c>
       <c r="K38" t="s" s="2">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="N38" s="2"/>
+        <v>324</v>
+      </c>
+      <c r="N38" t="s" s="2">
+        <v>325</v>
+      </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
         <v>75</v>
@@ -5714,7 +5886,7 @@
         <v>75</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -5726,21 +5898,21 @@
         <v>96</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>97</v>
+        <v>284</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>104</v>
+        <v>326</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>75</v>
+        <v>327</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>315</v>
+        <v>328</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5760,18 +5932,20 @@
         <v>75</v>
       </c>
       <c r="J39" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K39" t="s" s="2">
         <v>100</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>101</v>
+        <v>329</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>330</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>331</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>75</v>
@@ -5820,7 +5994,7 @@
         <v>75</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>103</v>
+        <v>328</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -5829,13 +6003,13 @@
         <v>84</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>104</v>
+        <v>332</v>
       </c>
       <c r="AL39" t="s" s="2">
         <v>75</v>
@@ -5843,21 +6017,21 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>316</v>
+        <v>333</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>75</v>
@@ -5866,19 +6040,19 @@
         <v>75</v>
       </c>
       <c r="J40" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>108</v>
+        <v>334</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>109</v>
+        <v>335</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>110</v>
+        <v>336</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -5916,34 +6090,34 @@
         <v>75</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>114</v>
+        <v>333</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>98</v>
+        <v>337</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>75</v>
@@ -5951,46 +6125,44 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>317</v>
+        <v>338</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
-        <v>318</v>
+        <v>75</v>
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>75</v>
       </c>
       <c r="I41" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J41" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>107</v>
+        <v>339</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>319</v>
+        <v>340</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>320</v>
+        <v>341</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="O41" t="s" s="2">
-        <v>212</v>
-      </c>
+        <v>342</v>
+      </c>
+      <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>75</v>
       </c>
@@ -6038,22 +6210,22 @@
         <v>75</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>321</v>
+        <v>338</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH41" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI41" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>98</v>
+        <v>343</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>75</v>
@@ -6061,10 +6233,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>322</v>
+        <v>344</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>322</v>
+        <v>344</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6084,19 +6256,19 @@
         <v>75</v>
       </c>
       <c r="J42" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>242</v>
+        <v>345</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>323</v>
+        <v>346</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>324</v>
+        <v>347</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>254</v>
+        <v>348</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6122,11 +6294,13 @@
         <v>75</v>
       </c>
       <c r="X42" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="Y42" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y42" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z42" t="s" s="2">
-        <v>325</v>
+        <v>75</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>75</v>
@@ -6144,7 +6318,7 @@
         <v>75</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>322</v>
+        <v>344</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -6156,10 +6330,10 @@
         <v>96</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>97</v>
+        <v>349</v>
       </c>
       <c r="AK42" t="s" s="2">
-        <v>310</v>
+        <v>350</v>
       </c>
       <c r="AL42" t="s" s="2">
         <v>75</v>
@@ -6167,10 +6341,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>326</v>
+        <v>351</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>326</v>
+        <v>351</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6181,7 +6355,7 @@
         <v>76</v>
       </c>
       <c r="G43" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H43" t="s" s="2">
         <v>75</v>
@@ -6193,16 +6367,16 @@
         <v>75</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>281</v>
+        <v>352</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>327</v>
+        <v>353</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>328</v>
+        <v>354</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>329</v>
+        <v>355</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6252,22 +6426,22 @@
         <v>75</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>326</v>
+        <v>351</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH43" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI43" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>97</v>
+        <v>356</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>330</v>
+        <v>357</v>
       </c>
       <c r="AL43" t="s" s="2">
         <v>75</v>
@@ -6275,10 +6449,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>331</v>
+        <v>358</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>331</v>
+        <v>358</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6301,16 +6475,16 @@
         <v>75</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>242</v>
+        <v>322</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>332</v>
+        <v>359</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>333</v>
+        <v>360</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>334</v>
+        <v>361</v>
       </c>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
@@ -6336,13 +6510,13 @@
         <v>75</v>
       </c>
       <c r="X44" t="s" s="2">
-        <v>158</v>
+        <v>75</v>
       </c>
       <c r="Y44" t="s" s="2">
-        <v>335</v>
+        <v>75</v>
       </c>
       <c r="Z44" t="s" s="2">
-        <v>336</v>
+        <v>75</v>
       </c>
       <c r="AA44" t="s" s="2">
         <v>75</v>
@@ -6360,7 +6534,7 @@
         <v>75</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>331</v>
+        <v>358</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -6372,10 +6546,10 @@
         <v>96</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>97</v>
+        <v>284</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>337</v>
+        <v>362</v>
       </c>
       <c r="AL44" t="s" s="2">
         <v>75</v>
@@ -6383,10 +6557,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>338</v>
+        <v>363</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>338</v>
+        <v>363</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6400,7 +6574,7 @@
         <v>77</v>
       </c>
       <c r="H45" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="I45" t="s" s="2">
         <v>75</v>
@@ -6412,13 +6586,13 @@
         <v>242</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>339</v>
+        <v>364</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>340</v>
+        <v>365</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>341</v>
+        <v>366</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6444,11 +6618,13 @@
         <v>75</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="Y45" s="2"/>
+        <v>158</v>
+      </c>
+      <c r="Y45" t="s" s="2">
+        <v>365</v>
+      </c>
       <c r="Z45" t="s" s="2">
-        <v>342</v>
+        <v>367</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>75</v>
@@ -6466,7 +6642,7 @@
         <v>75</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>338</v>
+        <v>363</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>76</v>
@@ -6481,7 +6657,7 @@
         <v>97</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>337</v>
+        <v>368</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>75</v>
@@ -6489,10 +6665,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>343</v>
+        <v>369</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>343</v>
+        <v>369</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6506,7 +6682,7 @@
         <v>77</v>
       </c>
       <c r="H46" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I46" t="s" s="2">
         <v>75</v>
@@ -6515,17 +6691,15 @@
         <v>75</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>242</v>
+        <v>370</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>344</v>
+        <v>371</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>345</v>
-      </c>
-      <c r="N46" t="s" s="2">
-        <v>346</v>
-      </c>
+        <v>372</v>
+      </c>
+      <c r="N46" s="2"/>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
         <v>75</v>
@@ -6550,13 +6724,13 @@
         <v>75</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>172</v>
+        <v>75</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>173</v>
+        <v>75</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>174</v>
+        <v>75</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>75</v>
@@ -6574,7 +6748,7 @@
         <v>75</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>343</v>
+        <v>369</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -6589,7 +6763,7 @@
         <v>97</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>347</v>
+        <v>104</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>75</v>
@@ -6597,10 +6771,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>348</v>
+        <v>373</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>348</v>
+        <v>373</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6611,7 +6785,7 @@
         <v>76</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>75</v>
@@ -6623,17 +6797,15 @@
         <v>75</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>242</v>
+        <v>100</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>349</v>
+        <v>101</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>350</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>254</v>
-      </c>
+        <v>102</v>
+      </c>
+      <c r="N47" s="2"/>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>75</v>
@@ -6658,13 +6830,13 @@
         <v>75</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>158</v>
+        <v>75</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>351</v>
+        <v>75</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>352</v>
+        <v>75</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>75</v>
@@ -6682,22 +6854,22 @@
         <v>75</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>348</v>
+        <v>103</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>96</v>
+        <v>75</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>337</v>
+        <v>104</v>
       </c>
       <c r="AL47" t="s" s="2">
         <v>75</v>
@@ -6705,21 +6877,21 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>353</v>
+        <v>374</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>353</v>
+        <v>374</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>75</v>
@@ -6731,15 +6903,17 @@
         <v>75</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>226</v>
+        <v>107</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>354</v>
+        <v>108</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>355</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>109</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>110</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>75</v>
@@ -6776,34 +6950,34 @@
         <v>75</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>75</v>
+        <v>111</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>75</v>
+        <v>112</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>75</v>
+        <v>113</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>353</v>
+        <v>114</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AK48" t="s" s="2">
-        <v>337</v>
+        <v>98</v>
       </c>
       <c r="AL48" t="s" s="2">
         <v>75</v>
@@ -6811,14 +6985,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>356</v>
+        <v>375</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>356</v>
+        <v>375</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>75</v>
+        <v>376</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -6831,24 +7005,26 @@
         <v>75</v>
       </c>
       <c r="I49" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>312</v>
+        <v>107</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>357</v>
+        <v>377</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>358</v>
+        <v>378</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="O49" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>212</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>75</v>
       </c>
@@ -6896,7 +7072,7 @@
         <v>75</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>356</v>
+        <v>379</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -6908,10 +7084,10 @@
         <v>96</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AK49" t="s" s="2">
-        <v>360</v>
+        <v>98</v>
       </c>
       <c r="AL49" t="s" s="2">
         <v>75</v>
@@ -6919,10 +7095,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>361</v>
+        <v>380</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>361</v>
+        <v>380</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6945,15 +7121,17 @@
         <v>75</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>100</v>
+        <v>242</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>101</v>
+        <v>381</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>102</v>
-      </c>
-      <c r="N50" s="2"/>
+        <v>382</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>313</v>
+      </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>75</v>
@@ -6978,13 +7156,11 @@
         <v>75</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y50" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="Y50" s="2"/>
       <c r="Z50" t="s" s="2">
-        <v>75</v>
+        <v>383</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>75</v>
@@ -7002,7 +7178,7 @@
         <v>75</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>103</v>
+        <v>380</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -7011,13 +7187,13 @@
         <v>84</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>75</v>
+        <v>96</v>
       </c>
       <c r="AJ50" t="s" s="2">
-        <v>75</v>
+        <v>97</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>104</v>
+        <v>368</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>75</v>
@@ -7025,21 +7201,21 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>362</v>
+        <v>384</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>362</v>
+        <v>384</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>106</v>
+        <v>75</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
         <v>76</v>
       </c>
       <c r="G51" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H51" t="s" s="2">
         <v>75</v>
@@ -7051,16 +7227,16 @@
         <v>75</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>107</v>
+        <v>339</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>108</v>
+        <v>385</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>109</v>
+        <v>386</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>110</v>
+        <v>387</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7098,34 +7274,34 @@
         <v>75</v>
       </c>
       <c r="AB51" t="s" s="2">
-        <v>111</v>
+        <v>75</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>114</v>
+        <v>384</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH51" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI51" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ51" t="s" s="2">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="AK51" t="s" s="2">
-        <v>98</v>
+        <v>388</v>
       </c>
       <c r="AL51" t="s" s="2">
         <v>75</v>
@@ -7133,14 +7309,14 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>363</v>
+        <v>389</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>363</v>
+        <v>389</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
-        <v>318</v>
+        <v>75</v>
       </c>
       <c r="E52" s="2"/>
       <c r="F52" t="s" s="2">
@@ -7153,26 +7329,24 @@
         <v>75</v>
       </c>
       <c r="I52" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="J52" t="s" s="2">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>107</v>
+        <v>242</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>319</v>
+        <v>390</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>320</v>
+        <v>391</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="O52" t="s" s="2">
-        <v>212</v>
-      </c>
+        <v>392</v>
+      </c>
+      <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
         <v>75</v>
       </c>
@@ -7196,13 +7370,13 @@
         <v>75</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>75</v>
+        <v>158</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>75</v>
+        <v>393</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>75</v>
+        <v>394</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>75</v>
@@ -7220,7 +7394,7 @@
         <v>75</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>321</v>
+        <v>389</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -7232,10 +7406,10 @@
         <v>96</v>
       </c>
       <c r="AJ52" t="s" s="2">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="AK52" t="s" s="2">
-        <v>98</v>
+        <v>395</v>
       </c>
       <c r="AL52" t="s" s="2">
         <v>75</v>
@@ -7243,10 +7417,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>364</v>
+        <v>396</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>364</v>
+        <v>396</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7260,7 +7434,7 @@
         <v>77</v>
       </c>
       <c r="H53" t="s" s="2">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="I53" t="s" s="2">
         <v>75</v>
@@ -7269,16 +7443,16 @@
         <v>75</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>168</v>
+        <v>242</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>365</v>
+        <v>397</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>366</v>
+        <v>398</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>273</v>
+        <v>399</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7304,13 +7478,11 @@
         <v>75</v>
       </c>
       <c r="X53" t="s" s="2">
-        <v>255</v>
-      </c>
-      <c r="Y53" t="s" s="2">
-        <v>367</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="Y53" s="2"/>
       <c r="Z53" t="s" s="2">
-        <v>368</v>
+        <v>400</v>
       </c>
       <c r="AA53" t="s" s="2">
         <v>75</v>
@@ -7328,7 +7500,7 @@
         <v>75</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>364</v>
+        <v>396</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -7343,7 +7515,7 @@
         <v>97</v>
       </c>
       <c r="AK53" t="s" s="2">
-        <v>360</v>
+        <v>395</v>
       </c>
       <c r="AL53" t="s" s="2">
         <v>75</v>
@@ -7351,10 +7523,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>369</v>
+        <v>401</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>369</v>
+        <v>401</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7365,7 +7537,7 @@
         <v>76</v>
       </c>
       <c r="G54" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H54" t="s" s="2">
         <v>75</v>
@@ -7377,15 +7549,17 @@
         <v>75</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>370</v>
+        <v>402</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>371</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>403</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>404</v>
+      </c>
       <c r="O54" s="2"/>
       <c r="P54" t="s" s="2">
         <v>75</v>
@@ -7410,13 +7584,13 @@
         <v>75</v>
       </c>
       <c r="X54" t="s" s="2">
-        <v>75</v>
+        <v>172</v>
       </c>
       <c r="Y54" t="s" s="2">
-        <v>75</v>
+        <v>173</v>
       </c>
       <c r="Z54" t="s" s="2">
-        <v>75</v>
+        <v>174</v>
       </c>
       <c r="AA54" t="s" s="2">
         <v>75</v>
@@ -7434,13 +7608,13 @@
         <v>75</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>369</v>
+        <v>401</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH54" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI54" t="s" s="2">
         <v>96</v>
@@ -7449,7 +7623,7 @@
         <v>97</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>360</v>
+        <v>405</v>
       </c>
       <c r="AL54" t="s" s="2">
         <v>75</v>
@@ -7457,10 +7631,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7471,7 +7645,7 @@
         <v>76</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>75</v>
@@ -7483,16 +7657,16 @@
         <v>75</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>373</v>
+        <v>242</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>374</v>
+        <v>407</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>375</v>
+        <v>408</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>376</v>
+        <v>313</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -7518,13 +7692,13 @@
         <v>75</v>
       </c>
       <c r="X55" t="s" s="2">
-        <v>75</v>
+        <v>158</v>
       </c>
       <c r="Y55" t="s" s="2">
-        <v>75</v>
+        <v>409</v>
       </c>
       <c r="Z55" t="s" s="2">
-        <v>75</v>
+        <v>410</v>
       </c>
       <c r="AA55" t="s" s="2">
         <v>75</v>
@@ -7542,13 +7716,13 @@
         <v>75</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>372</v>
+        <v>406</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>96</v>
@@ -7557,7 +7731,7 @@
         <v>97</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>360</v>
+        <v>395</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>75</v>
@@ -7565,10 +7739,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>377</v>
+        <v>411</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>377</v>
+        <v>411</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7591,17 +7765,15 @@
         <v>75</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>373</v>
+        <v>287</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>378</v>
+        <v>412</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="N56" t="s" s="2">
-        <v>376</v>
-      </c>
+        <v>413</v>
+      </c>
+      <c r="N56" s="2"/>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
         <v>75</v>
@@ -7650,7 +7822,7 @@
         <v>75</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>377</v>
+        <v>411</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
@@ -7665,7 +7837,7 @@
         <v>97</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>360</v>
+        <v>395</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>75</v>
@@ -7673,10 +7845,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>380</v>
+        <v>414</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>380</v>
+        <v>414</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -7699,15 +7871,17 @@
         <v>75</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>312</v>
+        <v>370</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>381</v>
+        <v>415</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="N57" s="2"/>
+        <v>416</v>
+      </c>
+      <c r="N57" t="s" s="2">
+        <v>417</v>
+      </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>75</v>
@@ -7756,7 +7930,7 @@
         <v>75</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>380</v>
+        <v>414</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>76</v>
@@ -7771,7 +7945,7 @@
         <v>97</v>
       </c>
       <c r="AK57" t="s" s="2">
-        <v>360</v>
+        <v>418</v>
       </c>
       <c r="AL57" t="s" s="2">
         <v>75</v>
@@ -7779,10 +7953,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>383</v>
+        <v>419</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>383</v>
+        <v>419</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -7885,10 +8059,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>384</v>
+        <v>420</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>384</v>
+        <v>420</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -7993,14 +8167,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>385</v>
+        <v>421</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>385</v>
+        <v>421</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>318</v>
+        <v>376</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8022,10 +8196,10 @@
         <v>107</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>319</v>
+        <v>377</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>320</v>
+        <v>378</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>110</v>
@@ -8080,7 +8254,7 @@
         <v>75</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>321</v>
+        <v>379</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -8103,10 +8277,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>386</v>
+        <v>422</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>386</v>
+        <v>422</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8114,10 +8288,10 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>75</v>
@@ -8129,16 +8303,16 @@
         <v>75</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>100</v>
+        <v>168</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>387</v>
+        <v>423</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>388</v>
+        <v>424</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>273</v>
+        <v>331</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8164,13 +8338,13 @@
         <v>75</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>75</v>
+        <v>235</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>75</v>
+        <v>425</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>75</v>
+        <v>426</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>75</v>
@@ -8188,13 +8362,13 @@
         <v>75</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>386</v>
+        <v>422</v>
       </c>
       <c r="AG61" t="s" s="2">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="AH61" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AI61" t="s" s="2">
         <v>96</v>
@@ -8203,7 +8377,7 @@
         <v>97</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>104</v>
+        <v>418</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>75</v>
@@ -8211,10 +8385,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>389</v>
+        <v>427</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>389</v>
+        <v>427</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8237,17 +8411,15 @@
         <v>75</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>390</v>
+        <v>287</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>391</v>
+        <v>428</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="N62" t="s" s="2">
-        <v>393</v>
-      </c>
+        <v>429</v>
+      </c>
+      <c r="N62" s="2"/>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
         <v>75</v>
@@ -8296,7 +8468,7 @@
         <v>75</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>389</v>
+        <v>427</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
@@ -8308,10 +8480,10 @@
         <v>96</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>394</v>
+        <v>97</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>360</v>
+        <v>418</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>75</v>
@@ -8319,10 +8491,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>395</v>
+        <v>430</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>395</v>
+        <v>430</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8345,16 +8517,16 @@
         <v>75</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>100</v>
+        <v>431</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>396</v>
+        <v>432</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>397</v>
+        <v>433</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>273</v>
+        <v>434</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -8404,7 +8576,7 @@
         <v>75</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>395</v>
+        <v>430</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>76</v>
@@ -8419,7 +8591,7 @@
         <v>97</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>360</v>
+        <v>418</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>75</v>
@@ -8427,10 +8599,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>398</v>
+        <v>435</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>398</v>
+        <v>435</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8441,7 +8613,7 @@
         <v>76</v>
       </c>
       <c r="G64" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H64" t="s" s="2">
         <v>75</v>
@@ -8453,16 +8625,16 @@
         <v>75</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>399</v>
+        <v>431</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>400</v>
+        <v>436</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>401</v>
+        <v>437</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>267</v>
+        <v>434</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -8512,29 +8684,891 @@
         <v>75</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>398</v>
+        <v>435</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AH64" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="AI64" t="s" s="2">
         <v>96</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>238</v>
+        <v>97</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>402</v>
+        <v>418</v>
       </c>
       <c r="AL64" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="65" hidden="true">
+      <c r="A65" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="B65" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="C65" s="2"/>
+      <c r="D65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E65" s="2"/>
+      <c r="F65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K65" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="L65" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M65" t="s" s="2">
+        <v>440</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+      <c r="P65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q65" s="2"/>
+      <c r="R65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE65" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF65" t="s" s="2">
+        <v>438</v>
+      </c>
+      <c r="AG65" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH65" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI65" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ65" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK65" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AL65" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="66" hidden="true">
+      <c r="A66" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="B66" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="C66" s="2"/>
+      <c r="D66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E66" s="2"/>
+      <c r="F66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K66" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L66" t="s" s="2">
+        <v>101</v>
+      </c>
+      <c r="M66" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
+      <c r="P66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q66" s="2"/>
+      <c r="R66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF66" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="AG66" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH66" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ66" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK66" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AL66" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="67" hidden="true">
+      <c r="A67" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="B67" t="s" s="2">
+        <v>442</v>
+      </c>
+      <c r="C67" s="2"/>
+      <c r="D67" t="s" s="2">
+        <v>106</v>
+      </c>
+      <c r="E67" s="2"/>
+      <c r="F67" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K67" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L67" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="M67" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="N67" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="O67" s="2"/>
+      <c r="P67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q67" s="2"/>
+      <c r="R67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB67" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="AC67" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="AD67" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE67" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="AF67" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="AG67" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH67" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI67" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ67" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AK67" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AL67" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="68" hidden="true">
+      <c r="A68" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="B68" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="C68" s="2"/>
+      <c r="D68" t="s" s="2">
+        <v>376</v>
+      </c>
+      <c r="E68" s="2"/>
+      <c r="F68" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I68" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="J68" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="K68" t="s" s="2">
+        <v>107</v>
+      </c>
+      <c r="L68" t="s" s="2">
+        <v>377</v>
+      </c>
+      <c r="M68" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="N68" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="O68" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="P68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q68" s="2"/>
+      <c r="R68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE68" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF68" t="s" s="2">
+        <v>379</v>
+      </c>
+      <c r="AG68" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH68" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI68" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ68" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="AK68" t="s" s="2">
+        <v>98</v>
+      </c>
+      <c r="AL68" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="69" hidden="true">
+      <c r="A69" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="B69" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="C69" s="2"/>
+      <c r="D69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E69" s="2"/>
+      <c r="F69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="G69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K69" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L69" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="M69" t="s" s="2">
+        <v>446</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="O69" s="2"/>
+      <c r="P69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q69" s="2"/>
+      <c r="R69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE69" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF69" t="s" s="2">
+        <v>444</v>
+      </c>
+      <c r="AG69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AH69" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI69" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ69" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK69" t="s" s="2">
+        <v>104</v>
+      </c>
+      <c r="AL69" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="70" hidden="true">
+      <c r="A70" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="B70" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="C70" s="2"/>
+      <c r="D70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E70" s="2"/>
+      <c r="F70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K70" t="s" s="2">
+        <v>270</v>
+      </c>
+      <c r="L70" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="M70" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="N70" t="s" s="2">
+        <v>273</v>
+      </c>
+      <c r="O70" s="2"/>
+      <c r="P70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q70" s="2"/>
+      <c r="R70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF70" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="AG70" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH70" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI70" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ70" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AK70" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AL70" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="71" hidden="true">
+      <c r="A71" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="B71" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="C71" s="2"/>
+      <c r="D71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E71" s="2"/>
+      <c r="F71" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="H71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K71" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="L71" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="M71" t="s" s="2">
+        <v>452</v>
+      </c>
+      <c r="N71" t="s" s="2">
+        <v>331</v>
+      </c>
+      <c r="O71" s="2"/>
+      <c r="P71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q71" s="2"/>
+      <c r="R71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF71" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="AG71" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH71" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="AI71" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ71" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AK71" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="AL71" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="72" hidden="true">
+      <c r="A72" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="B72" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="C72" s="2"/>
+      <c r="D72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E72" s="2"/>
+      <c r="F72" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="G72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="H72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K72" t="s" s="2">
+        <v>454</v>
+      </c>
+      <c r="L72" t="s" s="2">
+        <v>455</v>
+      </c>
+      <c r="M72" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="N72" t="s" s="2">
+        <v>325</v>
+      </c>
+      <c r="O72" s="2"/>
+      <c r="P72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Q72" s="2"/>
+      <c r="R72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="S72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE72" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF72" t="s" s="2">
+        <v>453</v>
+      </c>
+      <c r="AG72" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AH72" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AI72" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AJ72" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="AK72" t="s" s="2">
+        <v>457</v>
+      </c>
+      <c r="AL72" t="s" s="2">
         <v>75</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL64">
+  <autoFilter ref="A1:AL72">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -8544,7 +9578,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI63">
+  <conditionalFormatting sqref="A2:AI71">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-07T10:27:01+00:00</t>
+    <t>2024-03-12T12:54:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T12:54:34+00:00</t>
+    <t>2024-03-12T13:20:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:20:54+00:00</t>
+    <t>2024-03-12T13:39:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:39:01+00:00</t>
+    <t>2024-03-12T13:58:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T13:58:30+00:00</t>
+    <t>2024-03-12T14:02:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:02:45+00:00</t>
+    <t>2024-03-12T14:08:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:08:02+00:00</t>
+    <t>2024-03-12T14:13:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:13:18+00:00</t>
+    <t>2024-03-12T14:29:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T14:29:58+00:00</t>
+    <t>2024-03-12T16:57:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T16:57:02+00:00</t>
+    <t>2024-03-12T17:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-12T17:28:16+00:00</t>
+    <t>2024-03-13T08:21:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,13 +60,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T08:21:45+00:00</t>
+    <t>2024-03-13T15:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>ANS</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
   </si>
   <si>
     <t>Contact</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T15:21:15+00:00</t>
+    <t>2024-03-13T15:40:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-13T15:40:01+00:00</t>
+    <t>2024-03-15T14:37:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T13:53:07+00:00</t>
+    <t>2024-04-02T14:01:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.0-ballot-4</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-02T14:01:28+00:00</t>
+    <t>2024-04-03T13:55:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-08T12:41:20+00:00</t>
+    <t>2024-04-08T12:53:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-04-10T18:21:45+00:00</t>
+    <t>2024-04-18T13:43:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:10:14+00:00</t>
+    <t>2024-06-03T16:22:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:22:01+00:00</t>
+    <t>2024-06-03T16:23:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:23:50+00:00</t>
+    <t>2024-06-03T16:30:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-03T16:30:34+00:00</t>
+    <t>2024-06-05T12:07:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-05T12:07:44+00:00</t>
+    <t>2024-06-07T15:57:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -628,35 +628,35 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization</t>
-  </si>
-  <si>
-    <t>as-ext-healthcareservice-authorization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-healthcareservice-authorization}
+    <t>HealthcareService.extension:as-ext-authorization</t>
+  </si>
+  <si>
+    <t>as-ext-authorization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-authorization}
 </t>
   </si>
   <si>
-    <t>AS HealthcareService Autorization Extension</t>
-  </si>
-  <si>
-    <t>Extension créée dans le cadre de l'Annuaire Santé pour décrire les autorisations  des activités sanitaires, sociales, médico-sociales et d'enseignement et des équipements matériels lourds autorisés.</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization.id</t>
+    <t>AS Authorization Extension</t>
+  </si>
+  <si>
+    <t>Extension créée dans le cadre de l'Annuaire Santé pour décrire les autorisations des activités (HealthcareService) sanitaires, sociales, médico-sociales et d'enseignement et des équipements matériels (Device) lourds autorisés.</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:as-ext-authorization.id</t>
   </si>
   <si>
     <t>HealthcareService.extension.id</t>
   </si>
   <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization.extension</t>
+    <t>HealthcareService.extension:as-ext-authorization.extension</t>
   </si>
   <si>
     <t>HealthcareService.extension.extension</t>
   </si>
   <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization.extension:dateAuthorization</t>
+    <t>HealthcareService.extension:as-ext-authorization.extension:dateAuthorization</t>
   </si>
   <si>
     <t>dateAuthorization</t>
@@ -671,19 +671,19 @@
     <t>dateAutorisation</t>
   </si>
   <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization.extension:dateAuthorization.id</t>
+    <t>HealthcareService.extension:as-ext-authorization.extension:dateAuthorization.id</t>
   </si>
   <si>
     <t>HealthcareService.extension.extension.id</t>
   </si>
   <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization.extension:dateAuthorization.extension</t>
+    <t>HealthcareService.extension:as-ext-authorization.extension:dateAuthorization.extension</t>
   </si>
   <si>
     <t>HealthcareService.extension.extension.extension</t>
   </si>
   <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization.extension:dateAuthorization.url</t>
+    <t>HealthcareService.extension:as-ext-authorization.extension:dateAuthorization.url</t>
   </si>
   <si>
     <t>HealthcareService.extension.extension.url</t>
@@ -701,7 +701,7 @@
     <t>Extension.url</t>
   </si>
   <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization.extension:dateAuthorization.value[x]</t>
+    <t>HealthcareService.extension:as-ext-authorization.extension:dateAuthorization.value[x]</t>
   </si>
   <si>
     <t>HealthcareService.extension.extension.value[x]</t>
@@ -720,41 +720,41 @@
     <t>Extension.value[x]</t>
   </si>
   <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization.extension:periodAuthorization</t>
+    <t>HealthcareService.extension:as-ext-authorization.extension:periodAuthorization</t>
   </si>
   <si>
     <t>periodAuthorization</t>
   </si>
   <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization.extension:periodAuthorization.id</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization.extension:periodAuthorization.extension</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization.extension:periodAuthorization.url</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization.extension:periodAuthorization.value[x]</t>
+    <t>HealthcareService.extension:as-ext-authorization.extension:periodAuthorization.id</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:as-ext-authorization.extension:periodAuthorization.extension</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:as-ext-authorization.extension:periodAuthorization.url</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:as-ext-authorization.extension:periodAuthorization.value[x]</t>
   </si>
   <si>
     <t xml:space="preserve">Period
 </t>
   </si>
   <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization.extension:periodAuthorization.value[x].id</t>
+    <t>HealthcareService.extension:as-ext-authorization.extension:periodAuthorization.value[x].id</t>
   </si>
   <si>
     <t>HealthcareService.extension.extension.value[x].id</t>
   </si>
   <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization.extension:periodAuthorization.value[x].extension</t>
+    <t>HealthcareService.extension:as-ext-authorization.extension:periodAuthorization.value[x].extension</t>
   </si>
   <si>
     <t>HealthcareService.extension.extension.value[x].extension</t>
   </si>
   <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization.extension:periodAuthorization.value[x].start</t>
+    <t>HealthcareService.extension:as-ext-authorization.extension:periodAuthorization.value[x].start</t>
   </si>
   <si>
     <t>HealthcareService.extension.extension.value[x].start</t>
@@ -786,7 +786,7 @@
     <t>./low</t>
   </si>
   <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization.extension:periodAuthorization.value[x].end</t>
+    <t>HealthcareService.extension:as-ext-authorization.extension:periodAuthorization.value[x].end</t>
   </si>
   <si>
     <t>HealthcareService.extension.extension.value[x].end</t>
@@ -810,7 +810,7 @@
     <t>./high</t>
   </si>
   <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization.extension:dateUpdateAuthorization</t>
+    <t>HealthcareService.extension:as-ext-authorization.extension:dateUpdateAuthorization</t>
   </si>
   <si>
     <t>dateUpdateAuthorization</t>
@@ -819,19 +819,19 @@
     <t>Date de dernière mise à jour de l’autorisation.</t>
   </si>
   <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization.extension:dateUpdateAuthorization.id</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization.extension:dateUpdateAuthorization.extension</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization.extension:dateUpdateAuthorization.url</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization.extension:dateUpdateAuthorization.value[x]</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization.extension:deleteAuthorization</t>
+    <t>HealthcareService.extension:as-ext-authorization.extension:dateUpdateAuthorization.id</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:as-ext-authorization.extension:dateUpdateAuthorization.extension</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:as-ext-authorization.extension:dateUpdateAuthorization.url</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:as-ext-authorization.extension:dateUpdateAuthorization.value[x]</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:as-ext-authorization.extension:deleteAuthorization</t>
   </si>
   <si>
     <t>deleteAuthorization</t>
@@ -840,23 +840,23 @@
     <t>suppressionAutorisation</t>
   </si>
   <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization.extension:deleteAuthorization.id</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization.extension:deleteAuthorization.extension</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization.extension:deleteAuthorization.url</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization.extension:deleteAuthorization.value[x]</t>
+    <t>HealthcareService.extension:as-ext-authorization.extension:deleteAuthorization.id</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:as-ext-authorization.extension:deleteAuthorization.extension</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:as-ext-authorization.extension:deleteAuthorization.url</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:as-ext-authorization.extension:deleteAuthorization.value[x]</t>
   </si>
   <si>
     <t xml:space="preserve">boolean
 </t>
   </si>
   <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization.extension:dateLastInstallation</t>
+    <t>HealthcareService.extension:as-ext-authorization.extension:dateLastInstallation</t>
   </si>
   <si>
     <t>dateLastInstallation</t>
@@ -865,19 +865,19 @@
     <t>Date à laquelle le dernier constat d’installation des places est réalisé.</t>
   </si>
   <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization.extension:dateLastInstallation.id</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization.extension:dateLastInstallation.extension</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization.extension:dateLastInstallation.url</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization.extension:dateLastInstallation.value[x]</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization.extension:deleteInstallation</t>
+    <t>HealthcareService.extension:as-ext-authorization.extension:dateLastInstallation.id</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:as-ext-authorization.extension:dateLastInstallation.extension</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:as-ext-authorization.extension:dateLastInstallation.url</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:as-ext-authorization.extension:dateLastInstallation.value[x]</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:as-ext-authorization.extension:deleteInstallation</t>
   </si>
   <si>
     <t>deleteInstallation</t>
@@ -886,19 +886,19 @@
     <t>suppressionInstallation</t>
   </si>
   <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization.extension:deleteInstallation.id</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization.extension:deleteInstallation.extension</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization.extension:deleteInstallation.url</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization.extension:deleteInstallation.value[x]</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization.extension:sourceReportInstallation</t>
+    <t>HealthcareService.extension:as-ext-authorization.extension:deleteInstallation.id</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:as-ext-authorization.extension:deleteInstallation.extension</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:as-ext-authorization.extension:deleteInstallation.url</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:as-ext-authorization.extension:deleteInstallation.value[x]</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:as-ext-authorization.extension:sourceReportInstallation</t>
   </si>
   <si>
     <t>sourceReportInstallation</t>
@@ -907,16 +907,16 @@
     <t>Source ayant permis le constat d'installation.</t>
   </si>
   <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization.extension:sourceReportInstallation.id</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization.extension:sourceReportInstallation.extension</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization.extension:sourceReportInstallation.url</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization.extension:sourceReportInstallation.value[x]</t>
+    <t>HealthcareService.extension:as-ext-authorization.extension:sourceReportInstallation.id</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:as-ext-authorization.extension:sourceReportInstallation.extension</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:as-ext-authorization.extension:sourceReportInstallation.url</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:as-ext-authorization.extension:sourceReportInstallation.value[x]</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
@@ -929,16 +929,16 @@
     <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/ValueSet/VS-TRE-R301-SourceInformationInstallation</t>
   </si>
   <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization.url</t>
+    <t>HealthcareService.extension:as-ext-authorization.url</t>
   </si>
   <si>
     <t>HealthcareService.extension.url</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-healthcareservice-authorization</t>
-  </si>
-  <si>
-    <t>HealthcareService.extension:as-ext-healthcareservice-authorization.value[x]</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-authorization</t>
+  </si>
+  <si>
+    <t>HealthcareService.extension:as-ext-authorization.value[x]</t>
   </si>
   <si>
     <t>HealthcareService.extension.value[x]</t>
@@ -2372,9 +2372,9 @@
   <dimension ref="A1:AM181"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="109.5" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="103.2265625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="54.6171875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="36.5703125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="32.45703125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-07T15:57:22+00:00</t>
+    <t>2024-07-01T19:46:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-01T19:46:33+00:00</t>
+    <t>2024-07-09T08:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-09T08:44:23+00:00</t>
+    <t>2024-07-10T09:54:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -668,7 +668,7 @@
     <t>An Extension</t>
   </si>
   <si>
-    <t>dateAutorisation</t>
+    <t>ActiviteSociale.dateAutorisation</t>
   </si>
   <si>
     <t>HealthcareService.extension:as-ext-authorization.extension:dateAuthorization.id</t>
@@ -780,7 +780,7 @@
 per-1</t>
   </si>
   <si>
-    <t>datePremiereInstallation</t>
+    <t>ActiviteSociale.datePremiereInstallation</t>
   </si>
   <si>
     <t>./low</t>
@@ -837,7 +837,7 @@
     <t>deleteAuthorization</t>
   </si>
   <si>
-    <t>suppressionAutorisation</t>
+    <t>ActiviteSociale.suppressionAutorisation</t>
   </si>
   <si>
     <t>HealthcareService.extension:as-ext-authorization.extension:deleteAuthorization.id</t>
@@ -883,7 +883,7 @@
     <t>deleteInstallation</t>
   </si>
   <si>
-    <t>suppressionInstallation</t>
+    <t>ActiviteSociale.suppressionInstallation</t>
   </si>
   <si>
     <t>HealthcareService.extension:as-ext-authorization.extension:deleteInstallation.id</t>
@@ -1024,7 +1024,7 @@
 qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
-    <t>ageMinAutorisee</t>
+    <t>ActiviteSociale.ageMinAutorisee</t>
   </si>
   <si>
     <t>HealthcareService.extension:as-ext-patient-type.extension:authorizedAgeRange.value[x].high</t>
@@ -1045,7 +1045,7 @@
     <t>Range.high</t>
   </si>
   <si>
-    <t>ageMaxAutorisee</t>
+    <t>ActiviteSociale.ageMaxAutorisee</t>
   </si>
   <si>
     <t>HealthcareService.extension:as-ext-patient-type.extension:installedAgeRange</t>
@@ -1075,7 +1075,7 @@
     <t>HealthcareService.extension:as-ext-patient-type.extension:installedAgeRange.value[x].low</t>
   </si>
   <si>
-    <t>ageMaxInstallee</t>
+    <t>ActiviteSociale.ageMaxInstallee</t>
   </si>
   <si>
     <t>HealthcareService.extension:as-ext-patient-type.extension:installedAgeRange.value[x].high</t>
@@ -1118,7 +1118,7 @@
     <t>capacityAvailable</t>
   </si>
   <si>
-    <t>capaciteAutorisee</t>
+    <t>ActiviteSociale.capaciteAutorisee</t>
   </si>
   <si>
     <t>HealthcareService.extension:as-ext-supported-capacity.extension:capacityAvailable.id</t>
@@ -1143,7 +1143,7 @@
     <t>femaleCapacityAvailable</t>
   </si>
   <si>
-    <t>capaciteAutoriseeFemme</t>
+    <t>ActiviteSociale.capaciteAutoriseeFemme</t>
   </si>
   <si>
     <t>HealthcareService.extension:as-ext-supported-capacity.extension:femaleCapacityAvailable.id</t>
@@ -1164,7 +1164,7 @@
     <t>maleCapacityAvailable</t>
   </si>
   <si>
-    <t>capaciteAutoriseeHomme</t>
+    <t>ActiviteSociale.capaciteAutoriseeHomme</t>
   </si>
   <si>
     <t>HealthcareService.extension:as-ext-supported-capacity.extension:maleCapacityAvailable.id</t>
@@ -1185,7 +1185,7 @@
     <t>socialAssistanceCapacityAvailable</t>
   </si>
   <si>
-    <t>capaciteAutoriseeHabiliteAideSociale</t>
+    <t>ActiviteSociale.capaciteAutoriseeHabiliteAideSociale</t>
   </si>
   <si>
     <t>HealthcareService.extension:as-ext-supported-capacity.extension:socialAssistanceCapacityAvailable.id</t>
@@ -1206,7 +1206,7 @@
     <t>installedCapacity</t>
   </si>
   <si>
-    <t>capaciteInstallee</t>
+    <t>ActiviteSociale.capaciteInstallee</t>
   </si>
   <si>
     <t>HealthcareService.extension:as-ext-supported-capacity.extension:installedCapacity.id</t>
@@ -1227,7 +1227,7 @@
     <t>femaleInstalledCapacity</t>
   </si>
   <si>
-    <t>capaciteInstalleeFemme</t>
+    <t>ActiviteSociale.capaciteInstalleeFemme</t>
   </si>
   <si>
     <t>HealthcareService.extension:as-ext-supported-capacity.extension:femaleInstalledCapacity.id</t>
@@ -1248,7 +1248,7 @@
     <t>maleInstalledCapacity</t>
   </si>
   <si>
-    <t>capaciteInstalleeHomme</t>
+    <t>ActiviteSociale.capaciteInstalleeHomme</t>
   </si>
   <si>
     <t>HealthcareService.extension:as-ext-supported-capacity.extension:maleInstalledCapacity.id</t>
@@ -1269,7 +1269,7 @@
     <t>socialAssistanceInstalledCapacity</t>
   </si>
   <si>
-    <t>capaciteInstalleeHabiliteAideSociale</t>
+    <t>ActiviteSociale.capaciteInstalleeHabiliteAideSociale</t>
   </si>
   <si>
     <t>HealthcareService.extension:as-ext-supported-capacity.extension:socialAssistanceInstalledCapacity.id</t>
@@ -1609,7 +1609,7 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J136-DisciplineEquipementSocial-RASS/FHIR/JDV-J136-DisciplineEquipementSocial-RASS</t>
   </si>
   <si>
-    <t>discipineEquipementSociale</t>
+    <t>ActiviteSociale.discipineEquipementSociale</t>
   </si>
   <si>
     <t>.actrelationship[typeCode=COMP.act[classCode=ACT][moodCode=DEF].code</t>
@@ -1828,7 +1828,7 @@
     <t>https://mos.esante.gouv.fr/NOS/JDV_J137-Clientele-RASS/FHIR/JDV-J137-Clientele-RASS</t>
   </si>
   <si>
-    <t>clientele</t>
+    <t>ActiviteSociale.clientele</t>
   </si>
   <si>
     <t>HealthcareService.eligibility.comment</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.1</t>
+    <t>1.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T09:54:14+00:00</t>
+    <t>2024-07-10T10:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:00:25+00:00</t>
+    <t>2024-07-10T10:02:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:02:38+00:00</t>
+    <t>2024-07-10T10:13:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T10:13:33+00:00</t>
+    <t>2024-07-10T12:01:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T12:01:49+00:00</t>
+    <t>2024-07-10T12:37:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T12:37:24+00:00</t>
+    <t>2024-07-10T13:09:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:09:17+00:00</t>
+    <t>2024-07-10T13:09:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:09:58+00:00</t>
+    <t>2024-07-10T13:27:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-10T13:27:13+00:00</t>
+    <t>2024-07-11T14:15:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T14:15:05+00:00</t>
+    <t>2024-07-11T14:20:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0-snapshot</t>
+    <t>1.1.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T14:20:03+00:00</t>
+    <t>2024-07-11T15:32:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T15:32:47+00:00</t>
+    <t>2024-07-11T15:43:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T15:43:40+00:00</t>
+    <t>2024-07-11T16:04:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-11T16:04:15+00:00</t>
+    <t>2024-07-12T06:54:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-12T06:54:28+00:00</t>
+    <t>2024-07-12T07:24:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-27T17:01:01+00:00</t>
+    <t>2025-01-31T09:33:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T09:33:18+00:00</t>
+    <t>2025-02-03T16:26:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-03T16:26:04+00:00</t>
+    <t>2025-02-11T12:19:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:19:13+00:00</t>
+    <t>2025-02-11T12:46:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T12:46:26+00:00</t>
+    <t>2025-02-11T13:37:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T13:37:59+00:00</t>
+    <t>2025-02-11T14:09:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T14:09:44+00:00</t>
+    <t>2025-02-11T15:57:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T15:57:50+00:00</t>
+    <t>2025-02-11T16:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T16:04:30+00:00</t>
+    <t>2025-02-11T16:35:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-17T22:39:20+00:00</t>
+    <t>2025-02-24T08:37:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-24T08:37:03+00:00</t>
+    <t>2025-02-27T14:21:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T14:21:41+00:00</t>
+    <t>2025-02-27T14:23:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-27T14:23:05+00:00</t>
+    <t>2025-02-28T10:02:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-28T10:02:48+00:00</t>
+    <t>2025-03-05T17:59:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-05T17:59:44+00:00</t>
+    <t>2025-03-06T14:41:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T14:41:30+00:00</t>
+    <t>2025-03-06T14:56:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-06T14:56:25+00:00</t>
+    <t>2025-03-12T15:24:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-12T15:24:25+00:00</t>
+    <t>2025-03-18T14:02:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T14:02:39+00:00</t>
+    <t>2025-03-18T16:59:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-18T16:59:29+00:00</t>
+    <t>2025-03-21T10:50:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-1</t>
+    <t>1.2.0-snapshot-2</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-18T12:01:00+00:00</t>
+    <t>2026-06-19T13:53:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -449,7 +449,7 @@
     <t>as-ext-authorization</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-authorization|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-authorization|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -726,7 +726,7 @@
     <t>as-ext-installation</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-installation|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-installation|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -820,7 +820,7 @@
     <t>as-ext-patient-type</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-patient-type|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-patient-type|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -958,7 +958,7 @@
     <t>as-ext-supported-capacity</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-supported-capacity|1.2.0-snapshot-1}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-supported-capacity|1.2.0-snapshot-2}
 </t>
   </si>
   <si>
@@ -1406,7 +1406,7 @@
     <t>HealthcareService.providedBy</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.1.0|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-1)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-2)
 </t>
   </si>
   <si>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T13:53:04+00:00</t>
+    <t>2026-06-19T14:07:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T14:07:56+00:00</t>
+    <t>2026-06-23T09:20:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T09:20:47+00:00</t>
+    <t>2026-06-23T12:21:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-23T12:21:55+00:00</t>
+    <t>2026-06-26T10:36:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T10:36:05+00:00</t>
+    <t>2026-06-27T10:35:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-27T10:35:23+00:00</t>
+    <t>2026-06-30T07:59:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T07:59:11+00:00</t>
+    <t>2026-07-10T15:33:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.2.0-snapshot-2</t>
+    <t>1.2.0-snapshot-3</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T15:33:23+00:00</t>
+    <t>2026-07-10T15:46:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -449,7 +449,7 @@
     <t>as-ext-authorization</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-authorization|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-authorization|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -726,7 +726,7 @@
     <t>as-ext-installation</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-installation|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-installation|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -820,7 +820,7 @@
     <t>as-ext-patient-type</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-patient-type|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-patient-type|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -958,7 +958,7 @@
     <t>as-ext-supported-capacity</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-supported-capacity|1.2.0-snapshot-2}
+    <t xml:space="preserve">Extension {https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-supported-capacity|1.2.0-snapshot-3}
 </t>
   </si>
   <si>
@@ -1406,7 +1406,7 @@
     <t>HealthcareService.providedBy</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-2)
+    <t xml:space="preserve">Reference(https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-organization|2.2.0|https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-organization|1.2.0-snapshot-3)
 </t>
   </si>
   <si>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T15:46:03+00:00</t>
+    <t>2026-08-03T13:23:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T13:23:25+00:00</t>
+    <t>2026-08-03T14:28:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T14:28:09+00:00</t>
+    <t>2026-08-04T08:16:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
+++ b/main/ig/StructureDefinition-as-healthcareservice-social-equipment.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T08:16:57+00:00</t>
+    <t>2026-08-04T12:10:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
